--- a/docs/DBS6_Corrections_by_Situation_20260921-f066a8f0.xlsx
+++ b/docs/DBS6_Corrections_by_Situation_20260921-f066a8f0.xlsx
@@ -4068,12 +4068,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B · Out of focus, faded — investigate</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t xml:space="preserve"> cooling king size sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4083,64 +4083,64 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.69</v>
+        <v>5.93</v>
       </c>
       <c r="F55" t="n">
-        <v>407</v>
+        <v>85</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.496</v>
+        <v>0.094</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>25 → 25 → 5</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>mod 100→90%; TOS $3.16→$3.00</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Out of focus but converts (24% at top of search vs bar 10.5%): test TOS +10% $3.46 → $3.80 to 10-07; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B · Out of focus, faded — investigate</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bamboo Viscose Sheets Queen Size-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Cooling Sheets King Size-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4154,60 +4154,60 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6.09</v>
+        <v>5.69</v>
       </c>
       <c r="F56" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 16 → 9</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>60</v>
+        <v>7.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O56" t="n">
-        <v>6.36</v>
+        <v>3.74</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>mod 426→492%; base ↓11%; TOS $6.36→$6.39</t>
+          <t>mod 88→108%; TOS $3.74→$4.14</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Out of focus but converts (13% at top of search vs bar 10.5%): test TOS +10% $3.74 → $4.12 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B · Out of focus, faded — investigate</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Queen Sheets Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4217,64 +4217,64 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6.09</v>
+        <v>5.69</v>
       </c>
       <c r="F57" t="n">
-        <v>1010</v>
+        <v>407</v>
       </c>
       <c r="G57" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="I57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3</v>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>— → 44 → 7</t>
+          <t>25 → 25 → 5</t>
         </is>
       </c>
       <c r="M57" t="n">
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>4.72</v>
+        <v>3.16</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>mod 186→281%; base ↓25%</t>
+          <t>mod 100→90%; TOS $3.16→$3.00</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Out of focus but converts (15% at top of search vs bar 5.5%): test TOS +10% $3.16 → $3.48 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B · Out of focus, faded — investigate</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Queen Size Bamboo Sheets Set-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Queen Size Sheet Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4284,43 +4284,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>6.09</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.15</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>25 → 57 → —</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N58" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>6.07</v>
+        <v>5.17</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -4329,19 +4329,19 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Out of focus but converts (29% at top of search vs bar 13.3%): test TOS +10% $5.17 → $5.69 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B · Out of focus, leak — base cut</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Decolure Bamboo Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bamboo Sheets Queen Size-(HSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4351,64 +4351,64 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.52</v>
+        <v>4.93</v>
       </c>
       <c r="F59" t="n">
-        <v>745</v>
+        <v>1485</v>
       </c>
       <c r="G59" t="n">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="H59" t="n">
-        <v>0.533</v>
+        <v>0.783</v>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K59" t="n">
         <v>4</v>
       </c>
-      <c r="K59" t="n">
-        <v>23</v>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>17 → 34 → 5</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="N59" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="O59" t="n">
-        <v>4.24</v>
+        <v>4.56</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>mod 101→91%; TOS $4.24→$4.03</t>
+          <t>mod 283→383%; base ↓21%; TOS $4.56→$4.54</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Base −25% → $1.58; TOS price held via modifier</t>
+          <t>Out of focus but converts (21% at top of search vs bar 12.6%): test TOS +10% $4.56 → $5.01 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B · Out of focus, leak — base cut</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Red Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
+          <t>Bamboo Sheets Queen-(HSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4418,64 +4418,61 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.12</v>
+        <v>6.09</v>
       </c>
       <c r="F60" t="n">
-        <v>180</v>
+        <v>463</v>
       </c>
       <c r="G60" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
-        <v>0.412</v>
+        <v>0.425</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>32 → 52 → 5</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="N60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O60" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>mod 327→294%; TOS $4.78→$4.41</t>
+          <t>mod 88→79%</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Base −20% → $0.90; TOS price held via modifier</t>
+          <t>Out of focus but converts (22% vs bar 13.3%): no priced target on file — re-enable and set TOS at $6.09 as the test, to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bamboo Queen Size Sheet Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Sheets Twin Size-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4485,23 +4482,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="F61" t="n">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.225</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -4511,17 +4508,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>25 → 57 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>5.17</v>
+        <v>1.35</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -4530,19 +4527,19 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (11% at top of search vs bar 10.9%): test TOS +10% $1.35 → $1.49 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Queen Size-(HSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Viscose Sheets Queen Size-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4552,64 +4549,64 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.93</v>
+        <v>6.09</v>
       </c>
       <c r="F62" t="n">
-        <v>1485</v>
+        <v>120</v>
       </c>
       <c r="G62" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>0.783</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>17 → 34 → 5</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="N62" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O62" t="n">
-        <v>4.56</v>
+        <v>6.36</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>mod 283→383%; base ↓21%; TOS $4.56→$4.54</t>
+          <t>mod 426→492%; base ↓11%; TOS $6.36→$6.39</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (33% at top of search vs bar 6.4%): test TOS +10% $6.36 → $7.00 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Queen-(HSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Burgundy Sheets Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4619,56 +4616,59 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>6.09</v>
       </c>
       <c r="F63" t="n">
-        <v>463</v>
+        <v>26</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
-        <v>0.425</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>32 → 52 → 5</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="O63" t="n">
+        <v>5.71</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>mod 88→79%</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (21% at top of search vs bar 13.3%): test TOS +10% $5.71 → $6.28 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4728,19 +4728,19 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (19% at top of search vs bar 12.4%): test TOS +10% $4.81 → $5.29 to 10-07; advertise BAMBOO-FULL-CREME-6PCS</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cooling Sheets For Hot Sleepers-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Bed Sheets King-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4750,43 +4750,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>5.93</v>
       </c>
       <c r="F65" t="n">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>45 → 95 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O65" t="n">
-        <v>4.29</v>
+        <v>5.72</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -4795,19 +4795,19 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (11% at top of search vs bar 10.5%): test TOS +10% $5.72 → $6.29 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cooling Sheets For Night Sweats-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Bedsheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4824,36 +4824,36 @@
         <v>5.93</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>0.182</v>
+        <v>0.033</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>27 → 84 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O66" t="n">
-        <v>3.27</v>
+        <v>5.43</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -4862,19 +4862,19 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (17% at top of search vs bar 10.5%): test TOS +10% $5.43 → $5.98 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B · Out of focus, rank collapse — freeze</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Queen Size Sheets Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Sheet Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -4897,30 +4897,30 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.095</v>
+        <v>0.143</v>
       </c>
       <c r="I67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J67" t="n">
         <v>0.1</v>
       </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>28 → 64 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="O67" t="n">
-        <v>4.05</v>
+        <v>5.03</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -4929,19 +4929,19 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Freeze price and budget; investigate the rank loss</t>
+          <t>Out of focus but converts (12% at top of search vs bar 10.5%): test TOS +10% $5.03 → $5.54 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Antimicrobial Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Sheets For Hot Sleepers-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>45 → 95 → —</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -4996,19 +4996,19 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (22% at top of search vs bar 10.5%): test TOS +10% $4.29 → $4.72 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bamboo Bedding Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Sheets King Size Deep Pocket-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.091</v>
+        <v>0.022</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>4.96</v>
+        <v>3.34</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5063,19 +5063,19 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (18% at top of search vs bar 10.5%): test TOS +10% $3.34 → $3.68 to 10-07; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Queen Sheets-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Sheets Queen Deep Pockets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5085,23 +5085,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>5.93</v>
       </c>
       <c r="F70" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.571</v>
+        <v>0.681</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.08</v>
+        <v>3.84</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -5130,19 +5130,19 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (21% at top of search vs bar 10.5%): test TOS +10% $3.84 → $4.23 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets Full Size-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>Decolure Bamboo Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5152,26 +5152,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>5.93</v>
       </c>
       <c r="F71" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H71" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="K71" t="n">
         <v>2</v>
@@ -5182,34 +5182,34 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N71" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="O71" t="n">
-        <v>8.619999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 162→191%; base ↓10%; TOS $3.54→$3.55</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (42% at top of search vs bar 20.1%): test TOS +10% $3.54 → $3.89 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bamboo Cooling Sheets King Size-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Decolure Bamboo Sheets Queen Size-(VHSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5219,64 +5219,64 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VHSV</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.69</v>
+        <v>6.09</v>
       </c>
       <c r="F72" t="n">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.148</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
         <v>0.1</v>
       </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>— → 16 → 9</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>7.8</v>
+        <v>100</v>
       </c>
       <c r="N72" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.74</v>
+        <v>2.01</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>mod 88→108%; TOS $3.74→$4.14</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (27% at top of search vs bar 13.3%): test TOS +10% $2.01 → $2.22 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bamboo Deep Pocket Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Decolure Bamboo Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5286,29 +5286,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6.38</v>
+        <v>1.52</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>745</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5316,34 +5316,34 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O73" t="n">
-        <v>4.02</v>
+        <v>4.24</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 101→91%; TOS $4.24→$4.03</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (26% at top of search vs bar 5.8%): test TOS +10% $4.24 → $4.67 to 10-07</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bamboo Flat Sheet Only-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Deep Pocket Queen Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5357,19 +5357,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.26</v>
+        <v>7.3</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -5398,19 +5398,19 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (16% at top of search vs bar 13.3%): test TOS +10% $7.30 → $8.03 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bamboo Full Size Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>Queen Bamboo Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5420,29 +5420,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F75" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G75" t="n">
         <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>0.556</v>
+        <v>0.167</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0.2</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N75" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O75" t="n">
-        <v>6.44</v>
+        <v>6.06</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -5465,19 +5465,19 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (13% at top of search vs bar 13.3%): test TOS +10% $6.06 → $6.67 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bamboo Organic Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Queen Size Bamboo Sheets Set-[Bamboo|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5487,29 +5487,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O76" t="n">
-        <v>6.01</v>
+        <v>6.07</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -5532,19 +5532,19 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (28% at top of search vs bar 13.3%): test TOS +10% $6.07 → $6.67 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, converts — two-week test</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bamboo Queen Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Twin Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5558,60 +5558,60 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="F77" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>0.333</v>
+        <v>0.492</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 33 → —</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N77" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>6.07</v>
+        <v>5.04</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 130→117%; TOS $5.04→$4.75</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Out of focus but converts (27% at top of search vs bar 16.0%): test TOS +10% $5.04 → $5.54 to 10-07; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, faded — investigate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bamboo Queen Sheet Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Sheets Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5628,57 +5628,57 @@
         <v>6.09</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1010</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 44 → 7</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O78" t="n">
-        <v>2.82</v>
+        <v>4.72</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 186→281%; base ↓25%</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, leak — base cut</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bamboo Queen Sheets Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Red Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5692,25 +5692,25 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6.09</v>
+        <v>4.12</v>
       </c>
       <c r="F79" t="n">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H79" t="n">
-        <v>0.667</v>
+        <v>0.412</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5718,34 +5718,34 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O79" t="n">
-        <v>7.19</v>
+        <v>4.78</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 327→294%; TOS $4.78→$4.41</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Base −20% → $0.90; TOS price held via modifier</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, rank collapse — freeze</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bamboo Sheet Set Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Sheets For Night Sweats-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5759,39 +5759,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F80" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.706</v>
+        <v>0.182</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>27 → 84 → —</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N80" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.96</v>
+        <v>3.27</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -5800,19 +5800,19 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Freeze price and budget; investigate the rank loss</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B · Out of focus, thin — hold</t>
+          <t>B · Out of focus, rank collapse — freeze</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Cal King Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
+          <t>Queen Size Sheets Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5822,23 +5822,23 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="F81" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.375</v>
+        <v>0.095</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -5848,17 +5848,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>28 → 64 → —</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.41</v>
+        <v>4.05</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Freeze price and budget; investigate the rank loss</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Full Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>Antimicrobial Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5896,16 +5896,16 @@
         <v>6.38</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>6.01</v>
+        <v>4.17</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Queen Size Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Bedding Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5963,13 +5963,13 @@
         <v>6.09</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.68</v>
+        <v>4.96</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Twin Size-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Bamboo Cooling Queen Sheets-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6027,19 +6027,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F84" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.225</v>
+        <v>0.571</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1.35</v>
+        <v>4.08</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Twin-[Bamboo|Twin]-(MSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Bamboo Cooling Sheets Full Size-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6090,47 +6090,47 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>— → 27 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="O85" t="n">
-        <v>1.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>mod 55→121%; base ↓30%</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bamboo Sheets With Elastic Corner Straps-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bamboo Deep Pocket Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>6.38</v>
       </c>
       <c r="F86" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>6.45</v>
+        <v>4.02</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bamboo Viscose Bed Sheets Cooling-[Bamboo|Cooling]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Flat Sheet Only-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -6237,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -6254,13 +6254,13 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>5.65</v>
+        <v>3.26</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bed Sheets Bamboo Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Full Size Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6295,22 +6295,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>0.429</v>
+        <v>0.556</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O88" t="n">
-        <v>3.68</v>
+        <v>6.44</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Organic Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6362,16 +6362,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4.96</v>
+        <v>6.01</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Burgundy Bed Sheet Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
+          <t>Bamboo Queen Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6432,22 +6432,22 @@
         <v>6.09</v>
       </c>
       <c r="F90" t="n">
+        <v>15</v>
+      </c>
+      <c r="G90" t="n">
         <v>1</v>
       </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
         <v>20</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O90" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Burgundy Bed Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
+          <t>Bamboo Queen Sheet Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6499,13 +6499,13 @@
         <v>6.09</v>
       </c>
       <c r="F91" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Burgundy Sheets Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
+          <t>Bamboo Queen Sheets Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6566,22 +6566,22 @@
         <v>6.09</v>
       </c>
       <c r="F92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J92" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N92" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>5.71</v>
+        <v>7.19</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Buttery Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bamboo Sheet Set Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6630,22 +6630,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F93" t="n">
+        <v>17</v>
+      </c>
+      <c r="G93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -6659,10 +6659,10 @@
         <v>30</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O93" t="n">
-        <v>4.62</v>
+        <v>4.96</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>California King Sheet Sets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
+          <t>Bamboo Sheets Cal King Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6693,11 +6693,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F94" t="n">
         <v>16</v>
@@ -6706,10 +6706,10 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>4.26</v>
+        <v>4.41</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>California King Sheets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
+          <t>Bamboo Sheets Full Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6760,20 +6760,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -6790,13 +6790,13 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>4.94</v>
+        <v>6.01</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cool Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bamboo Sheets Queen Size Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6831,39 +6831,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F96" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>— → — → 10</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N96" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cooling Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Sheets Twin-[Bamboo|Twin]-(MSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6894,47 +6894,47 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
       <c r="F97" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H97" t="n">
-        <v>0.723</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 27 → —</t>
         </is>
       </c>
       <c r="M97" t="n">
         <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>6.61</v>
+        <v>1.69</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>holds</t>
+          <t>mod 55→121%; base ↓30%</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cooling Bamboo Sheets-[Bamboo|Cooling]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Bamboo Sheets With Elastic Corner Straps-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6961,29 +6961,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F98" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.32</v>
+        <v>0.773</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J98" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -6991,13 +6991,13 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N98" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>4.75</v>
+        <v>6.45</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cooling Bed Sheets Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>Bamboo Viscose Bed Sheets Cooling-[Bamboo|Cooling]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7035,13 +7035,13 @@
         <v>5.93</v>
       </c>
       <c r="F99" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.727</v>
+        <v>0.5</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>— → 32 → 10</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -7064,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1.9</v>
+        <v>5.65</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cooling Bed Sheets King-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bed Sheets Bamboo Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7095,29 +7095,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F100" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -7125,13 +7125,13 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="N100" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>5.72</v>
+        <v>3.68</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cooling Bedding-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Best Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7166,16 +7166,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.67</v>
+        <v>4.96</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cooling Bedsheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Burgundy Bed Sheet Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7233,25 +7233,25 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F102" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -7259,13 +7259,13 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>8.449999999999999</v>
+        <v>20</v>
       </c>
       <c r="N102" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>5.43</v>
+        <v>3.1</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cooling California King Sheets-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
+          <t>Burgundy Bed Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7296,23 +7296,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F103" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.182</v>
+        <v>0.9</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>4.69</v>
+        <v>3.29</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cooling Deep Pocket Queen Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Buttery Soft Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -7393,13 +7393,13 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>4.22</v>
+        <v>4.62</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cooling Full Size Sheets-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>California King Sheet Sets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7437,13 +7437,13 @@
         <v>5.93</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I105" t="n">
         <v>0.1</v>
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>4.93</v>
+        <v>4.26</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cooling King Bed Sheets-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>California King Sheets Cooling-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7504,13 +7504,13 @@
         <v>5.93</v>
       </c>
       <c r="F106" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>5.72</v>
+        <v>4.94</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cooling King Size Sheets Set-[Cooling|King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cool Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7571,33 +7571,36 @@
         <v>5.93</v>
       </c>
       <c r="F107" t="n">
+        <v>70</v>
+      </c>
+      <c r="G107" t="n">
         <v>4</v>
       </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → — → 10</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="O107" t="n">
+        <v>4.1</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -7618,7 +7621,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cooling Queen Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7628,20 +7631,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>5.93</v>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>0.723</v>
       </c>
       <c r="I108" t="n">
         <v>0.1</v>
@@ -7650,7 +7653,7 @@
         <v>0.1</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -7658,13 +7661,13 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="O108" t="n">
-        <v>5.42</v>
+        <v>6.61</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -7685,7 +7688,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cooling Sheet Set Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Bamboo Sheets-[Bamboo|Cooling]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7695,23 +7698,23 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>5.93</v>
       </c>
       <c r="F109" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>0.143</v>
+        <v>0.32</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0.1</v>
@@ -7725,13 +7728,13 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N109" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O109" t="n">
-        <v>5.03</v>
+        <v>4.75</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -7752,7 +7755,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cooling Sheets Bamboo-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Bed Sheets Full-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7762,43 +7765,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>5.93</v>
       </c>
       <c r="F110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>0.727</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 32 → 10</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N110" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>7.07</v>
+        <v>1.9</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -7819,7 +7822,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cooling Sheets Queen Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Bedding-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7836,16 +7839,16 @@
         <v>5.93</v>
       </c>
       <c r="F111" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -7859,13 +7862,13 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>4.66</v>
+        <v>3.67</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -7886,7 +7889,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deep Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling California King Sheets-[Cooling|California King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-CALIFKING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7896,23 +7899,23 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -7926,13 +7929,13 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2.82</v>
+        <v>4.69</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -7953,7 +7956,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deep Pocket Bamboo Sheets Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Deep Pocket Queen Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7967,10 +7970,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7993,13 +7996,13 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2.82</v>
+        <v>4.22</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8020,7 +8023,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deep Pocket Cooling Sheets-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling Full Size Sheets-[Cooling|Full]-(LSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8037,16 +8040,16 @@
         <v>5.93</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -8065,6 +8068,9 @@
       <c r="N114" t="n">
         <v>0</v>
       </c>
+      <c r="O114" t="n">
+        <v>4.93</v>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>holds</t>
@@ -8084,7 +8090,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deep Pocket Queen Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Cooling King Bed Sheets-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8094,23 +8100,23 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F115" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.333</v>
+        <v>0.462</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -8124,13 +8130,13 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>7.3</v>
+        <v>5.72</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -8151,7 +8157,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Full Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
+          <t>Cooling King Size Sheets Set-[Cooling|King]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8165,39 +8171,36 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="F116" t="n">
+        <v>4</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>— → — → —</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
         <v>10</v>
       </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>— → — → —</t>
-        </is>
-      </c>
-      <c r="M116" t="n">
-        <v>30</v>
-      </c>
       <c r="N116" t="n">
         <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>5.42</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -8218,7 +8221,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>King Cooling Sheets Deep Pocket-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Queen Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8235,19 +8238,19 @@
         <v>5.93</v>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -8261,10 +8264,10 @@
         <v>10</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O117" t="n">
-        <v>5.76</v>
+        <v>5.42</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -8285,7 +8288,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>King Sheets Bamboo Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Sheets Bamboo-[Bamboo|Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8295,29 +8298,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="F118" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -8325,13 +8328,13 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O118" t="n">
-        <v>6.01</v>
+        <v>7.07</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -8352,7 +8355,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>King Sheets Deep Pocket Cooling-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Cooling Sheets Queen Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8362,20 +8365,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>5.93</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="I119" t="n">
         <v>0.1</v>
@@ -8392,13 +8395,13 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>5.15</v>
+        <v>4.66</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -8419,7 +8422,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>King Size Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Deep Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8436,7 +8439,7 @@
         <v>6.38</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -8465,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -8486,7 +8489,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>King Size Bamboo Sheets Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Deep Pocket Bamboo Sheets Queen Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8500,10 +8503,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -8526,13 +8529,13 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>6.01</v>
+        <v>2.82</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -8553,7 +8556,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>King Size Cooling Sheets Set-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Deep Pocket Cooling Sheets-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8570,13 +8573,13 @@
         <v>5.93</v>
       </c>
       <c r="F122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -8617,7 +8620,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Natural Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Full Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-FULL-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8634,7 +8637,7 @@
         <v>6.38</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -8643,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -8663,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1.49</v>
+        <v>5.42</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -8684,7 +8687,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Organic Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Cooling Sheets Deep Pocket-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8694,29 +8697,29 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F124" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.485</v>
+        <v>0.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8724,13 +8727,13 @@
         </is>
       </c>
       <c r="M124" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N124" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>6.6</v>
+        <v>5.76</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -8751,7 +8754,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Queen Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Sheets Bamboo Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8765,19 +8768,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F125" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>0.214</v>
+        <v>0.222</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -8791,13 +8794,13 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>4.96</v>
+        <v>6.01</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -8818,7 +8821,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Queen Bamboo Sheets-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Sheets Deep Pocket Cooling-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8832,25 +8835,25 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F126" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J126" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8858,13 +8861,13 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N126" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>6.06</v>
+        <v>5.15</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -8885,7 +8888,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Queen Bed Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Size Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8899,16 +8902,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -8931,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -8952,7 +8955,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Queen Bed Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Size Bamboo Sheets Set Deep Pocket-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8966,22 +8969,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F128" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -8992,13 +8995,13 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N128" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>7.19</v>
+        <v>6.01</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -9019,7 +9022,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>King Size Cooling Sheets Set-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9036,19 +9039,19 @@
         <v>5.93</v>
       </c>
       <c r="F129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -9062,10 +9065,7 @@
         <v>10</v>
       </c>
       <c r="N129" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O129" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheets Deep Pockets-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Natural Bamboo Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -9115,10 +9115,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -9126,13 +9126,13 @@
         </is>
       </c>
       <c r="M130" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N130" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>5.54</v>
+        <v>1.49</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Queen Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Organic Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9163,40 +9163,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F131" t="n">
+        <v>33</v>
+      </c>
+      <c r="G131" t="n">
         <v>3</v>
       </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
       <c r="H131" t="n">
-        <v>0.333</v>
+        <v>0.485</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>— → — → 7</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M131" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>0.03</v>
+      </c>
+      <c r="O131" t="n">
+        <v>6.6</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -9217,7 +9220,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Queen Deep Pocket Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Bamboo Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9234,16 +9237,16 @@
         <v>6.09</v>
       </c>
       <c r="F132" t="n">
+        <v>14</v>
+      </c>
+      <c r="G132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0.214</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -9257,13 +9260,13 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N132" t="n">
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>4.62</v>
+        <v>4.96</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -9284,7 +9287,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Queen Extra Deep Pocket Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Bed Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9301,14 +9304,14 @@
         <v>6.09</v>
       </c>
       <c r="F133" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
         <v>1</v>
       </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
@@ -9324,13 +9327,13 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>3.26</v>
+        <v>2.79</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -9351,7 +9354,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Queen Sheets Bamboo Sheet Set-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Bed Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9361,27 +9364,27 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E134" t="n">
         <v>6.09</v>
       </c>
       <c r="F134" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G134" t="n">
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>0.435</v>
+        <v>0.316</v>
       </c>
       <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
         <v>0.1</v>
       </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
@@ -9391,13 +9394,13 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O134" t="n">
-        <v>7.12</v>
+        <v>7.19</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -9418,7 +9421,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Queen Sheets Bamboo-[Bamboo|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Cooling Sheet Set-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9428,43 +9431,43 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>— → 38 → 6</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M135" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O135" t="n">
-        <v>1.95</v>
+        <v>5.54</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -9485,7 +9488,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Queen Size Bed Sheets Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Cooling Sheets Deep Pockets-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9502,7 +9505,7 @@
         <v>5.93</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -9552,7 +9555,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Queen Size Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9569,36 +9572,33 @@
         <v>5.93</v>
       </c>
       <c r="F137" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → — → 7</t>
         </is>
       </c>
       <c r="M137" t="n">
         <v>10</v>
       </c>
       <c r="N137" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O137" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Queen Size Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Deep Pocket Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9636,22 +9636,22 @@
         <v>6.09</v>
       </c>
       <c r="F138" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>0.455</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -9659,13 +9659,13 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N138" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>7.19</v>
+        <v>4.62</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Red Queen Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
+          <t>Queen Extra Deep Pocket Sheet Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9703,13 +9703,13 @@
         <v>6.09</v>
       </c>
       <c r="F139" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sheets Bamboo King Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Queen Sheets Bamboo Sheet Set-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9763,20 +9763,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="F140" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0.222</v>
+        <v>0.435</v>
       </c>
       <c r="I140" t="n">
         <v>0.1</v>
@@ -9793,13 +9793,13 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>6.01</v>
+        <v>7.12</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sheets Queen Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Sheets Bamboo-[Bamboo|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9830,20 +9830,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>6.09</v>
       </c>
       <c r="F141" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -9856,17 +9856,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>— → 38 → 6</t>
         </is>
       </c>
       <c r="M141" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>6.01</v>
+        <v>1.95</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sheets Queen Size Bed Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Queen Size Bed Sheets Cooling-[Cooling|Queen]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9897,26 +9897,26 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F142" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K142" t="n">
         <v>1</v>
@@ -9927,13 +9927,13 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N142" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="O142" t="n">
-        <v>7.19</v>
+        <v>5.54</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Twin Bamboo Bed Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Queen Size Cooling Sheets-[Cooling|Queen]-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9964,29 +9964,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>MSV</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F143" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H143" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -9997,10 +9997,10 @@
         <v>10</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O143" t="n">
-        <v>0.6</v>
+        <v>5.54</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Twin Bamboo Sheets Set Cooling-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Queen Size Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10035,25 +10035,25 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0.455</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -10064,10 +10064,10 @@
         <v>20</v>
       </c>
       <c r="N144" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="O144" t="n">
-        <v>3.44</v>
+        <v>7.19</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Twin Size Cooling Sheets-[Cooling|Twin]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Red Queen Bed Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-BURGUNDY-6PCS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10102,25 +10102,25 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F145" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2</v>
+        <v>0.706</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N145" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>5.72</v>
+        <v>2.5</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>White Bamboo Queen Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Sheets Bamboo King Size Bed Set-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10169,19 +10169,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="F146" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>0.222</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -10201,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>2.16</v>
+        <v>6.01</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>White Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-CREME-6PCS</t>
+          <t>Sheets Queen Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10239,13 +10239,13 @@
         <v>6.09</v>
       </c>
       <c r="F147" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0.881</v>
+        <v>0.286</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -10262,13 +10262,13 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>5.78</v>
+        <v>6.01</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>White Cooling Sheets-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>Sheets Queen Size Bed Set Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10299,43 +10299,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F148" t="n">
+        <v>24</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>— → — → —</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
         <v>15</v>
       </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>— → — → —</t>
-        </is>
-      </c>
-      <c r="M148" t="n">
-        <v>10</v>
-      </c>
       <c r="N148" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="O148" t="n">
-        <v>5.03</v>
+        <v>7.19</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -10351,12 +10351,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> cooling king size sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Twin Bamboo Bed Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10366,20 +10366,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
       <c r="F149" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>0.094</v>
+        <v>0.455</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>8.449999999999999</v>
+        <v>10</v>
       </c>
       <c r="N149" t="n">
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>3.46</v>
+        <v>0.6</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -10411,19 +10411,19 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bamboo Sheets Pink-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-LIGHT PINK-6PCS</t>
+          <t>Twin Bamboo Sheets Set Cooling-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10440,22 +10440,22 @@
         <v>5.93</v>
       </c>
       <c r="F150" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>0.787</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -10463,34 +10463,34 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O150" t="n">
-        <v>6.96</v>
+        <v>3.44</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>mod 603→543%; TOS $6.96→$6.37</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Bamboo Twin Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Twin Size Cooling Sheets-[Cooling|Twin]-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10500,64 +10500,64 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F151" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H151" t="n">
-        <v>0.72</v>
+        <v>0.2</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>21 → 27 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M151" t="n">
         <v>10</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="O151" t="n">
-        <v>4.63</v>
+        <v>5.72</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>mod 426→383%; TOS $4.63→$4.25</t>
+          <t>holds</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cooling Sheets King Size Deep Pocket-[Cooling|King]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>White Bamboo Queen Sheets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10567,20 +10567,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>VLSV</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F152" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0.022</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -10597,13 +10597,13 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>3.34</v>
+        <v>2.16</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -10612,19 +10612,19 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cooling Sheets Queen Deep Pockets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>White Bamboo Sheets Queen-(VLSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-CREME-6PCS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10638,19 +10638,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5.93</v>
+        <v>6.09</v>
       </c>
       <c r="F153" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0.681</v>
+        <v>0.881</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>3.84</v>
+        <v>5.78</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
@@ -10679,19 +10679,19 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B · Out of focus, went dark — restore</t>
+          <t>B · Out of focus, thin — hold</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Decolure Bamboo Sheets Queen Size-(VHSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
+          <t>White Cooling Sheets-[Cooling]-(LSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10701,23 +10701,23 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VHSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="F154" t="n">
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.133</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J154" t="n">
         <v>0.1</v>
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O154" t="n">
-        <v>2.01</v>
+        <v>5.03</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
+          <t>Hold flat — no cut, no raise</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twin Sheets Bamboo-(VLSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
+          <t>Bamboo Sheets Pink-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-LIGHT PINK-6PCS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10772,19 +10772,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="F155" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H155" t="n">
-        <v>0.492</v>
+        <v>0.787</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -10794,21 +10794,21 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>— → 33 → —</t>
+          <t>— → — → —</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>5.04</v>
+        <v>6.96</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>mod 130→117%; TOS $5.04→$4.75</t>
+          <t>mod 603→543%; TOS $6.96→$6.37</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -10820,12 +10820,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>B · Out of focus, working — hold flat</t>
+          <t>B · Out of focus, went dark — restore</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Decolure Bamboo Sheets King Size-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE-6PCS</t>
+          <t>Bamboo Twin Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-WHITE-6PCS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10835,52 +10835,52 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VLSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
       <c r="F156" t="n">
         <v>82</v>
       </c>
       <c r="G156" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>— → — → —</t>
+          <t>21 → 27 → —</t>
         </is>
       </c>
       <c r="M156" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N156" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>3.54</v>
+        <v>4.63</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>mod 162→191%; base ↓10%; TOS $3.54→$3.55</t>
+          <t>mod 426→383%; TOS $4.63→$4.25</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Hold flat — no cut, no raise</t>
+          <t>Restore pre-cut prices and read next day; if already restored or never changed, check eligibility</t>
         </is>
       </c>
     </row>

--- a/docs/DBS6_Corrections_by_Situation_20260921-f066a8f0.xlsx
+++ b/docs/DBS6_Corrections_by_Situation_20260921-f066a8f0.xlsx
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $7.93 → $9.52; modifier 543%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $10.32 → $12.38; modifier 736%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $6.42 → $7.70; modifier 316%; re-point the ad to the serving child; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $8.34 → $10.01; modifier 441%; re-point the ad to the serving child; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $7.93 → $9.52; modifier 543%; daily read to 09-28</t>
+          <t>Push TOS +20% (no click requirement on file → +20% (a stated departure: the logic document would hold at the ceiling)): $10.32 → $12.38; modifier 736%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Restore pre-cut prices, then push TOS +30% (1% of required top-of-search clicks delivered → +30%): $4.80 → $6.24; base held; modifier would pass the 900% wall — base lifted as a stated trade: base $0.50 → $0.62; modifier 900%; daily read to 09-28</t>
+          <t>Restore pre-cut prices, then push TOS +30% (1% of required top-of-search clicks delivered → +30%): $4.80 → $6.24; base held; the modifier would pass the 900% wall, so the base carries the raise (0.50 → 0.62) at 900% — watch product-page share the next day: base $0.50 → $0.62; modifier 900%; daily read to 09-28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Out of focus but converts (24% at top of search vs bar 10.5%): test TOS +10% $3.46 → $3.80 to 10-07; restore the pre-cut base first</t>
+          <t>Out of focus but converts (24% at top of search vs bar 10.5%): test TOS +10% $3.46 → $3.80 to 10-07; budget $5.00/day; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Out of focus but converts (13% at top of search vs bar 10.5%): test TOS +10% $3.74 → $4.12 to 10-07</t>
+          <t>Out of focus but converts (13% at top of search vs bar 10.5%): test TOS +10% $3.74 → $4.12 to 10-07; budget $5.00/day</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Out of focus but converts (15% at top of search vs bar 5.5%): test TOS +10% $3.16 → $3.48 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
+          <t>Out of focus but converts (15% at top of search vs bar 5.5%): test TOS +10% $3.16 → $3.48 to 10-07; budget $5.00/day; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Out of focus but converts (29% at top of search vs bar 13.3%): test TOS +10% $5.17 → $5.69 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (29% at top of search vs bar 13.3%): test TOS +10% $5.17 → $5.69 to 10-07; budget $6.09/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Out of focus but converts (21% at top of search vs bar 12.6%): test TOS +10% $4.56 → $5.01 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (21% at top of search vs bar 12.6%): test TOS +10% $4.56 → $5.01 to 10-07; budget $5.37/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Out of focus but converts (11% at top of search vs bar 10.9%): test TOS +10% $1.35 → $1.49 to 10-07</t>
+          <t>Out of focus but converts (11% at top of search vs bar 10.9%): test TOS +10% $1.35 → $1.49 to 10-07; budget $5.00/day</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Out of focus but converts (33% at top of search vs bar 6.4%): test TOS +10% $6.36 → $7.00 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
+          <t>Out of focus but converts (33% at top of search vs bar 6.4%): test TOS +10% $6.36 → $7.00 to 10-07; budget $7.50/day; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Out of focus but converts (21% at top of search vs bar 13.3%): test TOS +10% $5.71 → $6.28 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (21% at top of search vs bar 13.3%): test TOS +10% $5.71 → $6.28 to 10-07; budget $6.73/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Out of focus but converts (19% at top of search vs bar 12.4%): test TOS +10% $4.81 → $5.29 to 10-07; advertise BAMBOO-FULL-CREME-6PCS</t>
+          <t>Out of focus but converts (19% at top of search vs bar 12.4%): test TOS +10% $4.81 → $5.29 to 10-07; budget $5.67/day; advertise BAMBOO-FULL-CREME-6PCS</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Out of focus but converts (11% at top of search vs bar 10.5%): test TOS +10% $5.72 → $6.29 to 10-07</t>
+          <t>Out of focus but converts (11% at top of search vs bar 10.5%): test TOS +10% $5.72 → $6.29 to 10-07; budget $6.74/day</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Out of focus but converts (17% at top of search vs bar 10.5%): test TOS +10% $5.43 → $5.98 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (17% at top of search vs bar 10.5%): test TOS +10% $5.43 → $5.98 to 10-07; budget $6.40/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Out of focus but converts (12% at top of search vs bar 10.5%): test TOS +10% $5.03 → $5.54 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (12% at top of search vs bar 10.5%): test TOS +10% $5.03 → $5.54 to 10-07; budget $5.93/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Out of focus but converts (22% at top of search vs bar 10.5%): test TOS +10% $4.29 → $4.72 to 10-07</t>
+          <t>Out of focus but converts (22% at top of search vs bar 10.5%): test TOS +10% $4.29 → $4.72 to 10-07; budget $5.06/day</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Out of focus but converts (18% at top of search vs bar 10.5%): test TOS +10% $3.34 → $3.68 to 10-07; restore the pre-cut base first</t>
+          <t>Out of focus but converts (18% at top of search vs bar 10.5%): test TOS +10% $3.34 → $3.68 to 10-07; budget $5.00/day; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Out of focus but converts (21% at top of search vs bar 10.5%): test TOS +10% $3.84 → $4.23 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
+          <t>Out of focus but converts (21% at top of search vs bar 10.5%): test TOS +10% $3.84 → $4.23 to 10-07; budget $5.00/day; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Out of focus but converts (42% at top of search vs bar 20.1%): test TOS +10% $3.54 → $3.89 to 10-07</t>
+          <t>Out of focus but converts (42% at top of search vs bar 20.1%): test TOS +10% $3.54 → $3.89 to 10-07; budget $5.00/day</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Out of focus but converts (27% at top of search vs bar 13.3%): test TOS +10% $2.01 → $2.22 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
+          <t>Out of focus but converts (27% at top of search vs bar 13.3%): test TOS +10% $2.01 → $2.22 to 10-07; budget $5.00/day; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Out of focus but converts (26% at top of search vs bar 5.8%): test TOS +10% $4.24 → $4.67 to 10-07</t>
+          <t>Out of focus but converts (26% at top of search vs bar 5.8%): test TOS +10% $4.24 → $4.67 to 10-07; budget $5.00/day</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Out of focus but converts (16% at top of search vs bar 13.3%): test TOS +10% $7.30 → $8.03 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (16% at top of search vs bar 13.3%): test TOS +10% $7.30 → $8.03 to 10-07; budget $8.60/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Out of focus but converts (13% at top of search vs bar 13.3%): test TOS +10% $6.06 → $6.67 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
+          <t>Out of focus but converts (13% at top of search vs bar 13.3%): test TOS +10% $6.06 → $6.67 to 10-07; budget $7.15/day; advertise BAMBOO-QUEEN-OLIVE-6PCS</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Out of focus but converts (28% at top of search vs bar 13.3%): test TOS +10% $6.07 → $6.67 to 10-07; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
+          <t>Out of focus but converts (28% at top of search vs bar 13.3%): test TOS +10% $6.07 → $6.67 to 10-07; budget $7.15/day; advertise BAMBOO-QUEEN-OLIVE-6PCS; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Out of focus but converts (27% at top of search vs bar 16.0%): test TOS +10% $5.04 → $5.54 to 10-07; restore the pre-cut base first</t>
+          <t>Out of focus but converts (27% at top of search vs bar 16.0%): test TOS +10% $5.04 → $5.54 to 10-07; budget $5.94/day; restore the pre-cut base first</t>
         </is>
       </c>
     </row>
